--- a/data/daily/2026-08/2026-08-25.xlsx
+++ b/data/daily/2026-08/2026-08-25.xlsx
@@ -1270,14 +1270,89 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1292,17 +1367,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="361950" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1317,85 +1392,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1525,132 +1525,132 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="990600" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>32,800원</t>
+          <t>29,900원</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>32,800원</t>
+          <t>29,900원</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -4054,7 +4054,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4062,34 +4062,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
+          <t>홀베리 레몬 비타C 500 10개입</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>홀베리</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1,500원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253277&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=030086178&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260422/eIhoZ9JSC5jbp33vSbZX987253277_00_01eIhoZ9JSC5jbp33vSbZX.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260312/RhgSqjNOPs6aCmkpEpj2030086178_00_00RhgSqjNOPs6aCmkpEpj2.jpg</t>
         </is>
       </c>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4112,19 +4112,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OHEcumxqCcJ047eosRhh600000145_00_00OHEcumxqCcJ047eosRhh.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4132,12 +4132,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
+          <t>[홍삼매니아] 자연관 홍삼정 에너타임 10포 10일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>자연관</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -4147,19 +4147,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602085&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=901762097&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260624/m6tznB24o1VYvw4vwVs3613602085_00_00m6tznB24o1VYvw4vwVs3.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250807/jJGIxkBNqg0FzVjNiyoV901762097_00_01jJGIxkBNqg0FzVjNiyoV.jpg</t>
         </is>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4167,12 +4167,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>안국약품 토비콤 루테인 지아잔틴 미니 30캡슐</t>
+          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>안국약품</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -4182,19 +4182,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=611982831&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000148&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250623/lX1R9GhsEUzz72XUg7VZ611982831_00_00lX1R9GhsEUzz72XUg7VZ.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/a7ohwSe3ShJimhwztOOK600000148_00_00a7ohwSe3ShJimhwztOOK.png</t>
         </is>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4202,27 +4202,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
+          <t>[신혜선 PICK] 동국제약 마데카 글루타치온 필름 12매 12일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000131&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911099&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/rCiQaBH4VQ1rKKr7rz83600000131_00_00rCiQaBH4VQ1rKKr7rz83.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260728/NbSqiy25P90IFlYxB3ux610911099_00_01NbSqiy25P90IFlYxB3ux.jpg</t>
         </is>
       </c>
     </row>
@@ -4237,12 +4237,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>락피도 티니핑 비타스틱 12포 12일분</t>
+          <t>종근당건강 락토핏 골드</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>락피도</t>
+          <t>종근당건강</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4252,19 +4252,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=951817119&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591580521&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260226/yrj6yZmrzRmjLCVxjDAB951817119_00_01yrj6yZmrzRmjLCVxjDAB.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260522/0jgRGoNZEcwwrbTgrqVw591580521_00_000jgRGoNZEcwwrbTgrqVw.jpg</t>
         </is>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>자연관 이뮨 멀티비타민 미네랄 4병</t>
+          <t>홀베리 유기농 10포 레몬생강즙</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>홀베리</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -4287,19 +4287,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602124&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=965923424&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20251216/mSQXyRQCV8ORV8edPm4n613602124_00_01mSQXyRQCV8ORV8edPm4n.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260305/0AapsR84t6vSDwtqGuP2965923424_00_000AapsR84t6vSDwtqGuP2.jpg</t>
         </is>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>오브맘 비타민C＆E 하루구미 30일분</t>
+          <t>안국약품 콜린 미오이노시톨 4000 10포</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>안국약품</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -4322,19 +4322,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602131&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=985472642&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250922/jrLxfLkWCczsCAsnqLoJ613602131_00_01jrLxfLkWCczsCAsnqLoJ.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250623/yivvMAKVS3Hyi026FPyX985472642_00_00yivvMAKVS3Hyi026FPyX.jpg</t>
         </is>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4342,34 +4342,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>대웅제약 마그네슘 30정 30일분</t>
+          <t>안국약품 토비콤 루테인 지아잔틴 미니 30캡슐</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>안국약품</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=611982831&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250623/lX1R9GhsEUzz72XUg7VZ611982831_00_00lX1R9GhsEUzz72XUg7VZ.jpg</t>
         </is>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
+          <t>오브맘 멀티비타민＆미네랄 하루구미 30일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>오브맘</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -4392,12 +4392,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602128&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250922/8husYxWOSsou1qKUi5IE613602128_00_018husYxWOSsou1qKUi5IE.jpg</t>
         </is>
       </c>
     </row>
@@ -4512,52 +4512,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>홍삼/인삼</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>비타민D</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
           <t>루테인/눈건강</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>루테인/눈건강</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>마그네슘</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>혈행</t>
         </is>
       </c>
     </row>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>홀베리</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -4579,42 +4579,42 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>자연관</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>동국제약</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>종근당건강</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>홀베리</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>안국약품</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>락피도</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>자연관</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>안국약품</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>오브맘</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
         </is>
       </c>
     </row>
@@ -4626,52 +4626,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
+          <t>홀베리 레몬 비타C 500 10개입</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
+          <t>[홍삼매니아] 자연관 홍삼정 에너타임 10포 10일분</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
+          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>[신혜선 PICK] 동국제약 마데카 글루타치온 필름 12매 12일분</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>종근당건강 락토핏 골드</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>홀베리 유기농 10포 레몬생강즙</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>안국약품 콜린 미오이노시톨 4000 10포</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
           <t>안국약품 토비콤 루테인 지아잔틴 미니 30캡슐</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>락피도 티니핑 비타스틱 12포 12일분</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>자연관 이뮨 멀티비타민 미네랄 4병</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>오브맘 비타민C＆E 하루구미 30일분</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 마그네슘 30정 30일분</t>
-        </is>
-      </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
+          <t>오브맘 멀티비타민＆미네랄 하루구미 30일분</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>1,500원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[8월 올영픽/감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>멜라메이트 식물성 멜라토닌 함유 구미 20/50구미</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -4955,24 +4955,24 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>16,900원</t>
+          <t>7,900원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000259167&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355463ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0025/A00000025916710ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4980,34 +4980,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>멜라메이트 식물성 멜라토닌 함유 구미 20/50구미</t>
+          <t>[8월 올영픽/한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>7,900원</t>
+          <t>32,900원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000259167&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0025/A00000025916710ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549616ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5015,34 +5015,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[8월 올영픽/한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>[8월 올영픽/감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>32,900원</t>
+          <t>16,900원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549616ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355463ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5050,34 +5050,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+          <t>[1등 유산균] 콜레올로지 컷 다이어트 유산균 20캡슐 (10일분)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>27,400원</t>
+          <t>25,500원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000229934&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022993407ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5085,34 +5085,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[8월 올영픽] 오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
+          <t>[8월 올영픽/서현PICK] 콜레올로지 PRO 600mg*30(+10)/60정 단품</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>55,900원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000193086&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000175634&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019308653ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017563485ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5120,34 +5120,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[8월 올영픽/1일 1정] 바이탈뷰티 메타그린 슬림업 30일 (+15일)</t>
+          <t>[8월 올영픽] 오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>바이탈뷰티</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>29,300원</t>
+          <t>55,900원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000248462&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000193086&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024846227ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019308653ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5155,34 +5155,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[8월 올영픽/서현PICK] 콜레올로지 PRO 600mg*30(+10)/60정 단품</t>
+          <t>[8월 올영픽/곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>생활약속</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17,900원</t>
+          <t>14,500원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000175634&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000180121&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017563485ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018012131ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5190,27 +5190,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[1등 유산균] 콜레올로지 컷 다이어트 유산균 20캡슐 (10일분)</t>
+          <t>[8월 올영픽/1일 1정] 바이탈뷰티 메타그린 슬림업 30일 (+15일)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>바이탈뷰티</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>25,500원</t>
+          <t>29,300원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000229934&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000248462&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022993407ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024846227ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
@@ -5340,37 +5340,37 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
           <t>멀티비타민/종합비타민</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
     </row>
@@ -5397,37 +5397,37 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
+          <t>프로뉴트리션</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
           <t>멜라메이트</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>프로뉴트리션</t>
-        </is>
-      </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>푸드올로지</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>오쏘몰</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>생활약속</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>바이탈뷰티</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>푸드올로지</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>푸드올로지</t>
         </is>
       </c>
     </row>
@@ -5449,42 +5449,42 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>멜라메이트 식물성 멜라토닌 함유 구미 20/50구미</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>[8월 올영픽/한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
           <t>[8월 올영픽/감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>멜라메이트 식물성 멜라토닌 함유 구미 20/50구미</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>[8월 올영픽/한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
-        </is>
-      </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+          <t>[1등 유산균] 콜레올로지 컷 다이어트 유산균 20캡슐 (10일분)</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
+          <t>[8월 올영픽/서현PICK] 콜레올로지 PRO 600mg*30(+10)/60정 단품</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
           <t>[8월 올영픽] 오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>[8월 올영픽/곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>[8월 올영픽/1일 1정] 바이탈뷰티 메타그린 슬림업 30일 (+15일)</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>[8월 올영픽/서현PICK] 콜레올로지 PRO 600mg*30(+10)/60정 단품</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>[1등 유산균] 콜레올로지 컷 다이어트 유산균 20캡슐 (10일분)</t>
         </is>
       </c>
     </row>
@@ -5506,42 +5506,42 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
+          <t>7,900원</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>32,900원</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
           <t>16,900원</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>7,900원</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>32,900원</t>
-        </is>
-      </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>27,400원</t>
+          <t>25,500원</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
+          <t>17,900원</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
           <t>55,900원</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>14,500원</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>29,300원</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>17,900원</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>25,500원</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5671,19 +5671,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>27.5</v>
+        <v>37.5</v>
       </c>
       <c r="D2" t="n">
         <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -5715,16 +5715,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
         <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -5733,7 +5733,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -5743,10 +5743,10 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -5755,29 +5755,29 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
         <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5799,7 +5799,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5821,7 +5821,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -5834,16 +5834,16 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
         <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -5853,34 +5853,12 @@
         <v>2.5</v>
       </c>
       <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
         <v>1</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
       <c r="F10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" t="n">
         <v>0</v>
       </c>
     </row>
